--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\MHH\now\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="13560" windowHeight="7485" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="支出明细表" sheetId="1" r:id="rId1"/>
@@ -29,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="97">
   <si>
     <t>梦幻西游 · 支出明细表（黄色行为新增录入区）</t>
   </si>
@@ -154,6 +159,9 @@
     <t>力宠龙鲤</t>
   </si>
   <si>
+    <t>力宠 （已卖出）</t>
+  </si>
+  <si>
     <t>购入法宠</t>
   </si>
   <si>
@@ -224,6 +232,12 @@
   </si>
   <si>
     <t>采购法宠卖出收入</t>
+  </si>
+  <si>
+    <t>龙鲤</t>
+  </si>
+  <si>
+    <t>卖出</t>
   </si>
   <si>
     <t>宠物小计</t>
@@ -323,7 +337,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -389,13 +403,6 @@
       <color rgb="FFC00000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -902,148 +909,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1848,7 +1855,7 @@
         <v>168</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:4">
@@ -1856,13 +1863,13 @@
         <v>35</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C35" s="8">
         <v>106</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:4">
@@ -1910,19 +1917,19 @@
         <v>15</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C41" s="21">
         <f>SUM(C31:C40)</f>
         <v>662</v>
       </c>
       <c r="D41" s="20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" ht="26" customHeight="1" spans="1:4">
       <c r="A42" s="16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
@@ -1930,49 +1937,49 @@
     </row>
     <row r="43" ht="16.5" spans="1:4">
       <c r="A43" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C43" s="8">
         <v>20</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44" ht="16.5" spans="1:4">
       <c r="A44" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C44" s="8">
         <v>35</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45" ht="16.5" spans="1:4">
       <c r="A45" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C45" s="8">
         <v>40.5</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:4">
       <c r="A46" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B46" s="18"/>
       <c r="C46" s="19"/>
@@ -1980,7 +1987,7 @@
     </row>
     <row r="47" ht="16.5" spans="1:4">
       <c r="A47" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47" s="18"/>
       <c r="C47" s="19"/>
@@ -1988,7 +1995,7 @@
     </row>
     <row r="48" ht="16.5" spans="1:4">
       <c r="A48" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B48" s="18"/>
       <c r="C48" s="19"/>
@@ -1996,7 +2003,7 @@
     </row>
     <row r="49" ht="16.5" spans="1:4">
       <c r="A49" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="19"/>
@@ -2004,7 +2011,7 @@
     </row>
     <row r="50" ht="16.5" spans="1:4">
       <c r="A50" s="18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="19"/>
@@ -2015,14 +2022,14 @@
         <v>15</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C51" s="21">
         <f>SUM(C43:C50)</f>
         <v>95.5</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53" ht="18" spans="1:4">
@@ -2030,24 +2037,24 @@
         <v>15</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C53" s="11">
         <f>C14+C29+C41+C51</f>
         <v>3959.4</v>
       </c>
       <c r="D53" s="22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55" ht="16.5" spans="1:4">
       <c r="A55" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="56" ht="16.5" spans="1:4">
       <c r="A56" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -2079,15 +2086,15 @@
   <sheetData>
     <row r="1" ht="38" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
@@ -2098,7 +2105,7 @@
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:4">
       <c r="A3" s="16" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -2106,29 +2113,35 @@
     </row>
     <row r="4" ht="16.5" spans="1:4">
       <c r="A4" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" s="8">
         <v>85.5</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:4">
       <c r="A5" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="18"/>
+        <v>63</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="19">
+        <v>161.5</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="6" ht="16.5" spans="1:4">
       <c r="A6" s="18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="19"/>
@@ -2136,7 +2149,7 @@
     </row>
     <row r="7" ht="16.5" spans="1:4">
       <c r="A7" s="18" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="19"/>
@@ -2147,11 +2160,11 @@
         <v>15</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C8" s="21">
         <f>SUM(C4:C7)</f>
-        <v>85.5</v>
+        <v>247</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>15</v>
@@ -2159,7 +2172,7 @@
     </row>
     <row r="9" ht="26" customHeight="1" spans="1:4">
       <c r="A9" s="16" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -2167,77 +2180,77 @@
     </row>
     <row r="10" ht="16.5" spans="1:4">
       <c r="A10" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C10" s="8">
         <v>202</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:4">
       <c r="A11" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C11" s="8">
         <v>67.45</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:4">
       <c r="A12" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C12" s="8">
         <v>67.45</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:4">
       <c r="A13" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C13" s="8">
         <v>66.78</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:4">
       <c r="A14" s="9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C14" s="8">
         <v>66.78</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:4">
       <c r="A15" s="18" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B15" s="18"/>
       <c r="C15" s="19"/>
@@ -2245,7 +2258,7 @@
     </row>
     <row r="16" ht="16.5" spans="1:4">
       <c r="A16" s="18" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B16" s="18"/>
       <c r="C16" s="19"/>
@@ -2253,7 +2266,7 @@
     </row>
     <row r="17" ht="16.5" spans="1:4">
       <c r="A17" s="18" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B17" s="18"/>
       <c r="C17" s="19"/>
@@ -2261,7 +2274,7 @@
     </row>
     <row r="18" ht="16.5" spans="1:4">
       <c r="A18" s="18" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B18" s="18"/>
       <c r="C18" s="19"/>
@@ -2269,7 +2282,7 @@
     </row>
     <row r="19" ht="16.5" spans="1:4">
       <c r="A19" s="18" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B19" s="18"/>
       <c r="C19" s="19"/>
@@ -2280,7 +2293,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C20" s="21">
         <f>SUM(C10:C19)</f>
@@ -2295,19 +2308,19 @@
         <v>15</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C22" s="11">
         <f>C8+C20</f>
-        <v>555.96</v>
+        <v>717.46</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:4">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2335,84 +2348,84 @@
   <sheetData>
     <row r="1" ht="38" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B3" s="5">
         <f>支出明细表!C53</f>
         <v>3959.4</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:3">
       <c r="A4" s="7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B4" s="8">
         <f>游戏变现收入明细表!C22</f>
-        <v>555.96</v>
+        <v>717.46</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="10" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B5" s="11">
         <f>B3-B4</f>
-        <v>3403.44</v>
+        <v>3241.94</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:3">
       <c r="A8" s="14" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:3">
       <c r="A9" s="14" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:3">
       <c r="A10" s="14" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:3">
       <c r="A11" s="14" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:3">
       <c r="A12" s="14" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:3">

--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="支出明细表" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="103">
   <si>
     <t>梦幻西游 · 支出明细表（黄色行为新增录入区）</t>
   </si>
@@ -240,6 +240,15 @@
     <t>卖出</t>
   </si>
   <si>
+    <t>吸血鬼</t>
+  </si>
+  <si>
+    <t>3JN胚子</t>
+  </si>
+  <si>
+    <t>物品 80环装</t>
+  </si>
+  <si>
     <t>宠物小计</t>
   </si>
   <si>
@@ -268,6 +277,15 @@
   </si>
   <si>
     <t>小菜4</t>
+  </si>
+  <si>
+    <t>小菜5</t>
+  </si>
+  <si>
+    <t>小菜6</t>
+  </si>
+  <si>
+    <t>小菜7</t>
   </si>
   <si>
     <t>物资小计</t>
@@ -2075,7 +2093,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2143,192 +2161,236 @@
       <c r="A6" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="18"/>
+      <c r="B6" s="18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="19">
+        <v>123.5</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="7" ht="16.5" spans="1:4">
       <c r="A7" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="18"/>
-    </row>
-    <row r="8" ht="15" spans="1:4">
-      <c r="A8" s="20" t="s">
+      <c r="B7" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="19">
+        <v>9.5</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:4">
+      <c r="A8" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="19">
+        <v>9.5</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" ht="15" spans="1:4">
+      <c r="A9" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="21">
-        <f>SUM(C4:C7)</f>
-        <v>247</v>
-      </c>
-      <c r="D8" s="20" t="s">
+      <c r="B9" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="21">
+        <f>SUM(C4:C8)</f>
+        <v>389.5</v>
+      </c>
+      <c r="D9" s="20" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1" spans="1:4">
-      <c r="A9" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-    </row>
-    <row r="10" ht="16.5" spans="1:4">
-      <c r="A10" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="8">
-        <v>202</v>
-      </c>
-      <c r="D10" s="9" t="s">
+    <row r="10" ht="26" customHeight="1" spans="1:4">
+      <c r="A10" s="16" t="s">
         <v>72</v>
       </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
     </row>
     <row r="11" ht="16.5" spans="1:4">
       <c r="A11" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C11" s="8">
-        <v>67.45</v>
+        <v>202</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:4">
       <c r="A12" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C12" s="8">
         <v>67.45</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" ht="16.5" spans="1:4">
       <c r="A13" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C13" s="8">
-        <v>66.78</v>
+        <v>67.45</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:4">
       <c r="A14" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C14" s="8">
         <v>66.78</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:4">
-      <c r="A15" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="18"/>
+      <c r="A15" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="8">
+        <v>66.78</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="16" ht="16.5" spans="1:4">
       <c r="A16" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="18"/>
+        <v>73</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="19">
+        <v>66.02</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
       <c r="A17" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="18"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="18"/>
+        <v>73</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="19">
+        <v>65.55</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
       <c r="A18" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="18"/>
+        <v>73</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="19">
+        <v>66.02</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
       <c r="A19" s="18" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B19" s="18"/>
       <c r="C19" s="19"/>
       <c r="D19" s="18"/>
     </row>
-    <row r="20" ht="15" spans="1:4">
-      <c r="A20" s="20" t="s">
+    <row r="20" ht="16.5" spans="1:4">
+      <c r="A20" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="18"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="18"/>
+    </row>
+    <row r="21" ht="15" spans="1:4">
+      <c r="A21" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="21">
-        <f>SUM(C10:C19)</f>
-        <v>470.46</v>
-      </c>
-      <c r="D20" s="20" t="s">
+      <c r="B21" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="21">
+        <f>SUM(C11:C20)</f>
+        <v>668.05</v>
+      </c>
+      <c r="D21" s="20" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" ht="18" spans="1:4">
-      <c r="A22" s="22" t="s">
+    <row r="23" ht="18" spans="1:4">
+      <c r="A23" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" s="11">
-        <f>C8+C20</f>
-        <v>717.46</v>
-      </c>
-      <c r="D22" s="22" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="24" ht="16.5" spans="1:4">
-      <c r="A24" s="14" t="s">
-        <v>81</v>
+      <c r="B23" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="11">
+        <f>C9+C21</f>
+        <v>1057.55</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:4">
+      <c r="A25" s="14" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A25:D25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2348,84 +2410,84 @@
   <sheetData>
     <row r="1" ht="38" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B3" s="5">
         <f>支出明细表!C53</f>
         <v>3959.4</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:3">
       <c r="A4" s="7" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B4" s="8">
-        <f>游戏变现收入明细表!C22</f>
-        <v>717.46</v>
+        <f>游戏变现收入明细表!C23</f>
+        <v>1057.55</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="10" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B5" s="11">
         <f>B3-B4</f>
-        <v>3241.94</v>
+        <v>2901.85</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="13" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:3">
       <c r="A8" s="14" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:3">
       <c r="A9" s="14" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:3">
       <c r="A10" s="14" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:3">
       <c r="A11" s="14" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:3">
       <c r="A12" s="14" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:3">

--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="12240" windowHeight="10410" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="支出明细表" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="121">
   <si>
     <t>梦幻西游 · 支出明细表（黄色行为新增录入区）</t>
   </si>
@@ -132,6 +132,24 @@
     <t>小号点卡 30*5支付优惠</t>
   </si>
   <si>
+    <t>8月21点卡</t>
+  </si>
+  <si>
+    <t>8月24点卡</t>
+  </si>
+  <si>
+    <t>8月27点卡</t>
+  </si>
+  <si>
+    <t>小号</t>
+  </si>
+  <si>
+    <t>8月26点卡</t>
+  </si>
+  <si>
+    <t>8月30点卡</t>
+  </si>
+  <si>
     <t>点卡小计</t>
   </si>
   <si>
@@ -147,12 +165,15 @@
     <t>蓝书力宠画魂</t>
   </si>
   <si>
+    <t>力宠（已卖出）</t>
+  </si>
+  <si>
+    <t>力宠蝴蝶仙子</t>
+  </si>
+  <si>
     <t>力宠</t>
   </si>
   <si>
-    <t>力宠蝴蝶仙子</t>
-  </si>
-  <si>
     <t>力宠吸血鬼</t>
   </si>
   <si>
@@ -168,6 +189,12 @@
     <t>法宠（后续卖出）</t>
   </si>
   <si>
+    <t xml:space="preserve">79龙鲤 </t>
+  </si>
+  <si>
+    <t>79龙鲤 2</t>
+  </si>
+  <si>
     <t>购宠小计</t>
   </si>
   <si>
@@ -246,6 +273,15 @@
     <t>3JN胚子</t>
   </si>
   <si>
+    <t>画魂  8月29</t>
+  </si>
+  <si>
+    <t>3JN胚子  8月10</t>
+  </si>
+  <si>
+    <t>蝴蝶仙子*2</t>
+  </si>
+  <si>
     <t>物品 80环装</t>
   </si>
   <si>
@@ -286,6 +322,24 @@
   </si>
   <si>
     <t>小菜7</t>
+  </si>
+  <si>
+    <t>小菜8   8月29</t>
+  </si>
+  <si>
+    <t>小菜    8月11</t>
+  </si>
+  <si>
+    <t>8月20</t>
+  </si>
+  <si>
+    <t>8月23</t>
+  </si>
+  <si>
+    <t>8月13</t>
+  </si>
+  <si>
+    <t>小菜9 8月27</t>
   </si>
   <si>
     <t>物资小计</t>
@@ -1470,7 +1524,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1769,251 +1823,289 @@
       <c r="A25" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="19"/>
+      <c r="B25" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="19">
+        <v>15</v>
+      </c>
       <c r="D25" s="18"/>
     </row>
     <row r="26" ht="16.5" spans="1:4">
       <c r="A26" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="18"/>
-      <c r="C26" s="19"/>
+      <c r="B26" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="19">
+        <v>1.05</v>
+      </c>
       <c r="D26" s="18"/>
     </row>
     <row r="27" ht="16.5" spans="1:4">
       <c r="A27" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="18"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="18"/>
+      <c r="B27" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="19">
+        <v>25</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="28" ht="16.5" spans="1:4">
       <c r="A28" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="18"/>
-      <c r="C28" s="19"/>
+      <c r="B28" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="19">
+        <v>20</v>
+      </c>
       <c r="D28" s="18"/>
     </row>
-    <row r="29" ht="15" spans="1:4">
-      <c r="A29" s="20" t="s">
+    <row r="29" ht="16.5" spans="1:4">
+      <c r="A29" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="19">
+        <v>30</v>
+      </c>
+      <c r="D29" s="18"/>
+    </row>
+    <row r="30" ht="16.5" spans="1:4">
+      <c r="A30" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="19">
+        <v>50</v>
+      </c>
+      <c r="D30" s="18"/>
+    </row>
+    <row r="31" ht="15" spans="1:4">
+      <c r="A31" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="21">
-        <f>SUM(C16:C28)</f>
-        <v>525</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" ht="26" customHeight="1" spans="1:4">
-      <c r="A30" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-    </row>
-    <row r="31" ht="16.5" spans="1:4">
-      <c r="A31" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C31" s="8">
-        <v>128</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="32" ht="16.5" spans="1:4">
-      <c r="A32" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" s="9" t="s">
+      <c r="B31" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="C32" s="8">
-        <v>140</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>37</v>
-      </c>
+      <c r="C31" s="21">
+        <f>SUM(C16:C30)</f>
+        <v>666.05</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1" spans="1:4">
+      <c r="A32" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
     </row>
     <row r="33" ht="16.5" spans="1:4">
       <c r="A33" s="9" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C33" s="8">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" ht="16.5" spans="1:4">
       <c r="A34" s="9" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C34" s="8">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" ht="16.5" spans="1:4">
       <c r="A35" s="9" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C35" s="8">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:4">
-      <c r="A36" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="18"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="18"/>
+      <c r="A36" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" s="8">
+        <v>168</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="37" ht="16.5" spans="1:4">
-      <c r="A37" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="18"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="18"/>
+      <c r="A37" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" s="8">
+        <v>106</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="38" ht="16.5" spans="1:4">
       <c r="A38" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38" s="18"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="18"/>
+        <v>41</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="19">
+        <v>68.25</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="39" ht="16.5" spans="1:4">
       <c r="A39" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="B39" s="18"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="18"/>
+        <v>41</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="19">
+        <v>65</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="40" ht="16.5" spans="1:4">
       <c r="A40" s="18" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B40" s="18"/>
       <c r="C40" s="19"/>
       <c r="D40" s="18"/>
     </row>
-    <row r="41" ht="15" spans="1:4">
-      <c r="A41" s="20" t="s">
+    <row r="41" ht="16.5" spans="1:4">
+      <c r="A41" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="18"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="18"/>
+    </row>
+    <row r="42" ht="16.5" spans="1:4">
+      <c r="A42" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="18"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="18"/>
+    </row>
+    <row r="43" ht="15" spans="1:4">
+      <c r="A43" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="C41" s="21">
-        <f>SUM(C31:C40)</f>
-        <v>662</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="42" ht="26" customHeight="1" spans="1:4">
-      <c r="A42" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-    </row>
-    <row r="43" ht="16.5" spans="1:4">
-      <c r="A43" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="C43" s="8">
-        <v>20</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="44" ht="16.5" spans="1:4">
-      <c r="A44" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C44" s="8">
-        <v>35</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>49</v>
-      </c>
+      <c r="B43" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C43" s="21">
+        <f>SUM(C33:C42)</f>
+        <v>795.25</v>
+      </c>
+      <c r="D43" s="20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1" spans="1:4">
+      <c r="A44" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
     </row>
     <row r="45" ht="16.5" spans="1:4">
       <c r="A45" s="9" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C45" s="8">
+        <v>20</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="1:4">
+      <c r="A46" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" s="8">
+        <v>35</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" spans="1:4">
+      <c r="A47" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47" s="8">
         <v>40.5</v>
       </c>
-      <c r="D45" s="9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="46" ht="16.5" spans="1:4">
-      <c r="A46" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B46" s="18"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="18"/>
-    </row>
-    <row r="47" ht="16.5" spans="1:4">
-      <c r="A47" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B47" s="18"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="18"/>
+      <c r="D47" s="9" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="48" ht="16.5" spans="1:4">
       <c r="A48" s="18" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B48" s="18"/>
       <c r="C48" s="19"/>
@@ -2021,7 +2113,7 @@
     </row>
     <row r="49" ht="16.5" spans="1:4">
       <c r="A49" s="18" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="19"/>
@@ -2029,50 +2121,66 @@
     </row>
     <row r="50" ht="16.5" spans="1:4">
       <c r="A50" s="18" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="19"/>
       <c r="D50" s="18"/>
     </row>
-    <row r="51" ht="15" spans="1:4">
-      <c r="A51" s="20" t="s">
+    <row r="51" ht="16.5" spans="1:4">
+      <c r="A51" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" s="18"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="18"/>
+    </row>
+    <row r="52" ht="16.5" spans="1:4">
+      <c r="A52" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="18"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="18"/>
+    </row>
+    <row r="53" ht="15" spans="1:4">
+      <c r="A53" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B51" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C51" s="21">
-        <f>SUM(C43:C50)</f>
+      <c r="B53" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C53" s="21">
+        <f>SUM(C45:C52)</f>
         <v>95.5</v>
       </c>
-      <c r="D51" s="20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="53" ht="18" spans="1:4">
-      <c r="A53" s="22" t="s">
+      <c r="D53" s="20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="55" ht="18" spans="1:4">
+      <c r="A55" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B53" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="C53" s="11">
-        <f>C14+C29+C41+C51</f>
-        <v>3959.4</v>
-      </c>
-      <c r="D53" s="22" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="55" ht="16.5" spans="1:4">
-      <c r="A55" s="14" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="56" ht="16.5" spans="1:4">
-      <c r="A56" s="14" t="s">
-        <v>58</v>
+      <c r="B55" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C55" s="11">
+        <f>C14+C31+C43+C53</f>
+        <v>4233.7</v>
+      </c>
+      <c r="D55" s="22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="57" ht="16.5" spans="1:4">
+      <c r="A57" s="14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" spans="1:4">
+      <c r="A58" s="14" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -2080,10 +2188,10 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="A58:D58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2093,7 +2201,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2104,15 +2212,15 @@
   <sheetData>
     <row r="1" ht="38" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
@@ -2123,7 +2231,7 @@
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:4">
       <c r="A3" s="16" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -2131,266 +2239,376 @@
     </row>
     <row r="4" ht="16.5" spans="1:4">
       <c r="A4" s="9" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C4" s="8">
         <v>85.5</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:4">
       <c r="A5" s="18" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C5" s="19">
         <v>161.5</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:4">
       <c r="A6" s="18" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C6" s="19">
         <v>123.5</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:4">
       <c r="A7" s="18" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C7" s="19">
         <v>9.5</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:4">
       <c r="A8" s="18" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C8" s="19">
+        <v>115</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:4">
+      <c r="A9" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="19">
         <v>9.5</v>
       </c>
-      <c r="D8" s="18" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" ht="15" spans="1:4">
-      <c r="A9" s="20" t="s">
+      <c r="D9" s="18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:4">
+      <c r="A10" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="19">
+        <v>66.5</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:4">
+      <c r="A11" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="19">
+        <v>9.5</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:4">
+      <c r="A12" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="21">
-        <f>SUM(C4:C8)</f>
-        <v>389.5</v>
-      </c>
-      <c r="D9" s="20" t="s">
+      <c r="B12" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="21">
+        <f>SUM(C4:C11)</f>
+        <v>580.5</v>
+      </c>
+      <c r="D12" s="20" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1" spans="1:4">
-      <c r="A10" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-    </row>
-    <row r="11" ht="16.5" spans="1:4">
-      <c r="A11" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="8">
-        <v>202</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:4">
-      <c r="A12" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="8">
-        <v>67.45</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:4">
-      <c r="A13" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" s="8">
-        <v>67.45</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>77</v>
-      </c>
+    <row r="13" ht="26" customHeight="1" spans="1:4">
+      <c r="A13" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
     </row>
     <row r="14" ht="16.5" spans="1:4">
       <c r="A14" s="9" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C14" s="8">
-        <v>66.78</v>
+        <v>202</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:4">
       <c r="A15" s="9" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C15" s="8">
+        <v>67.45</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:4">
+      <c r="A16" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="8">
+        <v>67.45</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:4">
+      <c r="A17" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C17" s="8">
         <v>66.78</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:4">
-      <c r="A16" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" s="19">
-        <v>66.02</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:4">
-      <c r="A17" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" s="19">
-        <v>65.55</v>
-      </c>
       <c r="D17" s="9" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
-      <c r="A18" s="18" t="s">
-        <v>73</v>
+      <c r="A18" s="9" t="s">
+        <v>85</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" s="19">
-        <v>66.02</v>
+        <v>92</v>
+      </c>
+      <c r="C18" s="8">
+        <v>66.78</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
       <c r="A19" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="18"/>
+        <v>85</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="19">
+        <v>66.02</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
       <c r="A20" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="B20" s="18"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="18"/>
-    </row>
-    <row r="21" ht="15" spans="1:4">
-      <c r="A21" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="19">
+        <v>65.55</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:4">
+      <c r="A21" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="19">
+        <v>66.02</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:4">
+      <c r="A22" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" s="19">
+        <v>69.2</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:4">
+      <c r="A23" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" s="19">
+        <v>68</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="1:4">
+      <c r="A24" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C24" s="19">
+        <v>41</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="1:4">
+      <c r="A25" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="19">
+        <v>67.7</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="1:4">
+      <c r="A26" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="19">
+        <v>68</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" spans="1:4">
+      <c r="A27" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C27" s="19">
+        <v>41.82</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" ht="15" spans="1:4">
+      <c r="A28" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" s="21">
-        <f>SUM(C11:C20)</f>
-        <v>668.05</v>
-      </c>
-      <c r="D21" s="20" t="s">
+      <c r="B28" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" s="21">
+        <f>SUM(C14:C27)</f>
+        <v>1023.77</v>
+      </c>
+      <c r="D28" s="20" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="23" ht="18" spans="1:4">
-      <c r="A23" s="22" t="s">
+    <row r="30" ht="18" spans="1:4">
+      <c r="A30" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" s="11">
-        <f>C9+C21</f>
-        <v>1057.55</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" spans="1:4">
-      <c r="A25" s="14" t="s">
-        <v>87</v>
+      <c r="B30" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="11">
+        <f>C12+C28</f>
+        <v>1604.27</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" spans="1:4">
+      <c r="A32" s="14" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2410,84 +2628,84 @@
   <sheetData>
     <row r="1" ht="38" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="B3" s="5">
-        <f>支出明细表!C53</f>
-        <v>3959.4</v>
+        <f>支出明细表!C55</f>
+        <v>4233.7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:3">
       <c r="A4" s="7" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="B4" s="8">
-        <f>游戏变现收入明细表!C23</f>
-        <v>1057.55</v>
+        <f>游戏变现收入明细表!C30</f>
+        <v>1604.27</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="10" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="B5" s="11">
         <f>B3-B4</f>
-        <v>2901.85</v>
+        <v>2629.43</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="13" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:3">
       <c r="A8" s="14" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:3">
       <c r="A9" s="14" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:3">
       <c r="A10" s="14" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:3">
       <c r="A11" s="14" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:3">
       <c r="A12" s="14" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:3">

--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="12240" windowHeight="10410" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="支出明细表" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="123">
   <si>
     <t>梦幻西游 · 支出明细表（黄色行为新增录入区）</t>
   </si>
@@ -193,6 +193,12 @@
   </si>
   <si>
     <t>79龙鲤 2</t>
+  </si>
+  <si>
+    <t>须弥画魂高魔心带套0903</t>
+  </si>
+  <si>
+    <t>法宠</t>
   </si>
   <si>
     <t>购宠小计</t>
@@ -2018,9 +2024,15 @@
       <c r="A40" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="18"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="18"/>
+      <c r="B40" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="19">
+        <v>409</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="41" ht="16.5" spans="1:4">
       <c r="A41" s="18" t="s">
@@ -2043,19 +2055,19 @@
         <v>15</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C43" s="21">
         <f>SUM(C33:C42)</f>
-        <v>795.25</v>
+        <v>1204.25</v>
       </c>
       <c r="D43" s="20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1" spans="1:4">
       <c r="A44" s="16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -2063,49 +2075,49 @@
     </row>
     <row r="45" ht="16.5" spans="1:4">
       <c r="A45" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C45" s="8">
         <v>20</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" ht="16.5" spans="1:4">
       <c r="A46" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C46" s="8">
         <v>35</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" ht="16.5" spans="1:4">
       <c r="A47" s="9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C47" s="8">
         <v>40.5</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:4">
       <c r="A48" s="18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B48" s="18"/>
       <c r="C48" s="19"/>
@@ -2113,7 +2125,7 @@
     </row>
     <row r="49" ht="16.5" spans="1:4">
       <c r="A49" s="18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="19"/>
@@ -2121,7 +2133,7 @@
     </row>
     <row r="50" ht="16.5" spans="1:4">
       <c r="A50" s="18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="19"/>
@@ -2129,7 +2141,7 @@
     </row>
     <row r="51" ht="16.5" spans="1:4">
       <c r="A51" s="18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="19"/>
@@ -2137,7 +2149,7 @@
     </row>
     <row r="52" ht="16.5" spans="1:4">
       <c r="A52" s="18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B52" s="18"/>
       <c r="C52" s="19"/>
@@ -2148,14 +2160,14 @@
         <v>15</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C53" s="21">
         <f>SUM(C45:C52)</f>
         <v>95.5</v>
       </c>
       <c r="D53" s="20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:4">
@@ -2163,24 +2175,24 @@
         <v>15</v>
       </c>
       <c r="B55" s="22" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C55" s="11">
         <f>C14+C31+C43+C53</f>
-        <v>4233.7</v>
+        <v>4642.7</v>
       </c>
       <c r="D55" s="22" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:4">
       <c r="A57" s="14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:4">
       <c r="A58" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -2212,15 +2224,15 @@
   <sheetData>
     <row r="1" ht="38" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
@@ -2231,7 +2243,7 @@
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:4">
       <c r="A3" s="16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -2239,114 +2251,114 @@
     </row>
     <row r="4" ht="16.5" spans="1:4">
       <c r="A4" s="9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C4" s="8">
         <v>85.5</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:4">
       <c r="A5" s="18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C5" s="19">
         <v>161.5</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:4">
       <c r="A6" s="18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C6" s="19">
         <v>123.5</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:4">
       <c r="A7" s="18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C7" s="19">
         <v>9.5</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:4">
       <c r="A8" s="18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C8" s="19">
         <v>115</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:4">
       <c r="A9" s="18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C9" s="19">
         <v>9.5</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:4">
       <c r="A10" s="18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C10" s="19">
         <v>66.5</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:4">
       <c r="A11" s="18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C11" s="19">
         <v>9.5</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" ht="15" spans="1:4">
@@ -2354,7 +2366,7 @@
         <v>15</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C12" s="21">
         <f>SUM(C4:C11)</f>
@@ -2366,7 +2378,7 @@
     </row>
     <row r="13" ht="26" customHeight="1" spans="1:4">
       <c r="A13" s="16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -2374,198 +2386,198 @@
     </row>
     <row r="14" ht="16.5" spans="1:4">
       <c r="A14" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C14" s="8">
         <v>202</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:4">
       <c r="A15" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C15" s="8">
         <v>67.45</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:4">
       <c r="A16" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C16" s="8">
         <v>67.45</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
       <c r="A17" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C17" s="8">
         <v>66.78</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
       <c r="A18" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C18" s="8">
         <v>66.78</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
       <c r="A19" s="18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C19" s="19">
         <v>66.02</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
       <c r="A20" s="18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C20" s="19">
         <v>65.55</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
       <c r="A21" s="18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C21" s="19">
         <v>66.02</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
       <c r="A22" s="18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C22" s="19">
         <v>69.2</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:4">
       <c r="A23" s="18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C23" s="19">
         <v>68</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:4">
       <c r="A24" s="18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C24" s="19">
         <v>41</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:4">
       <c r="A25" s="18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C25" s="19">
         <v>67.7</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:4">
       <c r="A26" s="18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C26" s="19">
         <v>68</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:4">
       <c r="A27" s="18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C27" s="19">
         <v>41.82</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" ht="15" spans="1:4">
@@ -2573,7 +2585,7 @@
         <v>15</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C28" s="21">
         <f>SUM(C14:C27)</f>
@@ -2588,19 +2600,19 @@
         <v>15</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C30" s="11">
         <f>C12+C28</f>
         <v>1604.27</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:4">
       <c r="A32" s="14" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2628,84 +2640,84 @@
   <sheetData>
     <row r="1" ht="38" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B3" s="5">
         <f>支出明细表!C55</f>
-        <v>4233.7</v>
+        <v>4642.7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:3">
       <c r="A4" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B4" s="8">
         <f>游戏变现收入明细表!C30</f>
         <v>1604.27</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B5" s="11">
         <f>B3-B4</f>
-        <v>2629.43</v>
+        <v>3038.43</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:3">
       <c r="A8" s="14" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:3">
       <c r="A9" s="14" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:3">
       <c r="A10" s="14" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:3">
       <c r="A11" s="14" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:3">
       <c r="A12" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:3">

--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="124">
   <si>
     <t>梦幻西游 · 支出明细表（黄色行为新增录入区）</t>
   </si>
@@ -148,6 +148,9 @@
   </si>
   <si>
     <t>8月30点卡</t>
+  </si>
+  <si>
+    <t>9月月卡</t>
   </si>
   <si>
     <t>点卡小计</t>
@@ -1530,7 +1533,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D58"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1892,248 +1895,254 @@
         <v>19</v>
       </c>
       <c r="B30" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="19">
+        <v>290</v>
+      </c>
+      <c r="D30" s="18">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" ht="16.5" spans="1:4">
+      <c r="A31" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="19">
+      <c r="C31" s="19">
         <v>50</v>
       </c>
-      <c r="D30" s="18"/>
-    </row>
-    <row r="31" ht="15" spans="1:4">
-      <c r="A31" s="20" t="s">
+      <c r="D31" s="18"/>
+    </row>
+    <row r="32" ht="16.5" spans="1:4">
+      <c r="A32" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" s="20"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="20"/>
+    </row>
+    <row r="33" ht="15" spans="1:4">
+      <c r="A33" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C31" s="21">
-        <f>SUM(C16:C30)</f>
-        <v>666.05</v>
-      </c>
-      <c r="D31" s="20" t="s">
+      <c r="B33" s="20" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="32" ht="26" customHeight="1" spans="1:4">
-      <c r="A32" s="16" t="s">
+      <c r="C33" s="21">
+        <f>SUM(C16:C31)</f>
+        <v>956.05</v>
+      </c>
+      <c r="D33" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-    </row>
-    <row r="33" ht="16.5" spans="1:4">
-      <c r="A33" s="9" t="s">
+    </row>
+    <row r="34" ht="26" customHeight="1" spans="1:4">
+      <c r="A34" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C33" s="8">
-        <v>128</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" ht="16.5" spans="1:4">
-      <c r="A34" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="8">
-        <v>140</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>45</v>
-      </c>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
     </row>
     <row r="35" ht="16.5" spans="1:4">
       <c r="A35" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C35" s="8">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" ht="16.5" spans="1:4">
       <c r="A36" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C36" s="8">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37" ht="16.5" spans="1:4">
       <c r="A37" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B37" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="8">
+        <v>120</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" ht="16.5" spans="1:4">
+      <c r="A38" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C38" s="8">
+        <v>168</v>
+      </c>
+      <c r="D38" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C37" s="8">
+    </row>
+    <row r="39" ht="16.5" spans="1:4">
+      <c r="A39" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" s="8">
         <v>106</v>
       </c>
-      <c r="D37" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="38" ht="16.5" spans="1:4">
-      <c r="A38" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="18" t="s">
+      <c r="D39" s="9" t="s">
         <v>51</v>
-      </c>
-      <c r="C38" s="19">
-        <v>68.25</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="39" ht="16.5" spans="1:4">
-      <c r="A39" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="C39" s="19">
-        <v>65</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="40" ht="16.5" spans="1:4">
       <c r="A40" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C40" s="19">
-        <v>409</v>
-      </c>
-      <c r="D40" s="18" t="s">
-        <v>54</v>
+        <v>68.25</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="41" ht="16.5" spans="1:4">
       <c r="A41" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="18"/>
+        <v>42</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="19">
+        <v>65</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="42" ht="16.5" spans="1:4">
       <c r="A42" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="18"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="18"/>
-    </row>
-    <row r="43" ht="15" spans="1:4">
-      <c r="A43" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C42" s="19">
+        <v>409</v>
+      </c>
+      <c r="D42" s="18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" spans="1:4">
+      <c r="A43" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="18"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="18"/>
+    </row>
+    <row r="44" ht="16.5" spans="1:4">
+      <c r="A44" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B44" s="18"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="18"/>
+    </row>
+    <row r="45" ht="15" spans="1:4">
+      <c r="A45" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" s="21">
-        <f>SUM(C33:C42)</f>
+      <c r="B45" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45" s="21">
+        <f>SUM(C35:C44)</f>
         <v>1204.25</v>
       </c>
-      <c r="D43" s="20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="44" ht="26" customHeight="1" spans="1:4">
-      <c r="A44" s="16" t="s">
+      <c r="D45" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-    </row>
-    <row r="45" ht="16.5" spans="1:4">
-      <c r="A45" s="9" t="s">
+    </row>
+    <row r="46" ht="26" customHeight="1" spans="1:4">
+      <c r="A46" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="B45" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C45" s="8">
-        <v>20</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="46" ht="16.5" spans="1:4">
-      <c r="A46" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C46" s="8">
-        <v>35</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>60</v>
-      </c>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
     </row>
     <row r="47" ht="16.5" spans="1:4">
       <c r="A47" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B47" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47" s="8">
+        <v>20</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="1:4">
+      <c r="A48" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B48" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C47" s="8">
+      <c r="C48" s="8">
+        <v>35</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" spans="1:4">
+      <c r="A49" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C49" s="8">
         <v>40.5</v>
       </c>
-      <c r="D47" s="9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="48" ht="16.5" spans="1:4">
-      <c r="A48" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="B48" s="18"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="18"/>
-    </row>
-    <row r="49" ht="16.5" spans="1:4">
-      <c r="A49" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="B49" s="18"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="18"/>
+      <c r="D49" s="9" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="50" ht="16.5" spans="1:4">
       <c r="A50" s="18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="19"/>
@@ -2141,7 +2150,7 @@
     </row>
     <row r="51" ht="16.5" spans="1:4">
       <c r="A51" s="18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="19"/>
@@ -2149,50 +2158,66 @@
     </row>
     <row r="52" ht="16.5" spans="1:4">
       <c r="A52" s="18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B52" s="18"/>
       <c r="C52" s="19"/>
       <c r="D52" s="18"/>
     </row>
-    <row r="53" ht="15" spans="1:4">
-      <c r="A53" s="20" t="s">
+    <row r="53" ht="16.5" spans="1:4">
+      <c r="A53" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="18"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="18"/>
+    </row>
+    <row r="54" ht="16.5" spans="1:4">
+      <c r="A54" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" s="18"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="18"/>
+    </row>
+    <row r="55" ht="15" spans="1:4">
+      <c r="A55" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B53" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="C53" s="21">
-        <f>SUM(C45:C52)</f>
+      <c r="B55" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C55" s="21">
+        <f>SUM(C47:C54)</f>
         <v>95.5</v>
       </c>
-      <c r="D53" s="20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="55" ht="18" spans="1:4">
-      <c r="A55" s="22" t="s">
+      <c r="D55" s="20" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="57" ht="18" spans="1:4">
+      <c r="A57" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B55" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C55" s="11">
-        <f>C14+C31+C43+C53</f>
-        <v>4642.7</v>
-      </c>
-      <c r="D55" s="22" t="s">
+      <c r="B57" s="22" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="57" ht="16.5" spans="1:4">
-      <c r="A57" s="14" t="s">
+      <c r="C57" s="11">
+        <f>C14+C33+C45+C55</f>
+        <v>4932.7</v>
+      </c>
+      <c r="D57" s="22" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="58" ht="16.5" spans="1:4">
-      <c r="A58" s="14" t="s">
+    <row r="59" ht="16.5" spans="1:4">
+      <c r="A59" s="14" t="s">
         <v>69</v>
+      </c>
+    </row>
+    <row r="60" ht="16.5" spans="1:4">
+      <c r="A60" s="14" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -2200,10 +2225,10 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A44:D44"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A60:D60"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2224,15 +2249,15 @@
   <sheetData>
     <row r="1" ht="38" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
@@ -2243,7 +2268,7 @@
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:4">
       <c r="A3" s="16" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -2251,114 +2276,114 @@
     </row>
     <row r="4" ht="16.5" spans="1:4">
       <c r="A4" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4" s="8">
         <v>85.5</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:4">
       <c r="A5" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C5" s="19">
         <v>161.5</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:4">
       <c r="A6" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" s="19">
         <v>123.5</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:4">
       <c r="A7" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C7" s="19">
         <v>9.5</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:4">
       <c r="A8" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" s="19">
         <v>115</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:4">
       <c r="A9" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" s="19">
         <v>9.5</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:4">
       <c r="A10" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C10" s="19">
         <v>66.5</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:4">
       <c r="A11" s="18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C11" s="19">
         <v>9.5</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" ht="15" spans="1:4">
@@ -2366,7 +2391,7 @@
         <v>15</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C12" s="21">
         <f>SUM(C4:C11)</f>
@@ -2378,7 +2403,7 @@
     </row>
     <row r="13" ht="26" customHeight="1" spans="1:4">
       <c r="A13" s="16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
@@ -2386,198 +2411,198 @@
     </row>
     <row r="14" ht="16.5" spans="1:4">
       <c r="A14" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C14" s="8">
         <v>202</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" ht="16.5" spans="1:4">
       <c r="A15" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C15" s="8">
         <v>67.45</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:4">
       <c r="A16" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C16" s="8">
         <v>67.45</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
       <c r="A17" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C17" s="8">
         <v>66.78</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
       <c r="A18" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C18" s="8">
         <v>66.78</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
       <c r="A19" s="18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C19" s="19">
         <v>66.02</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
       <c r="A20" s="18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C20" s="19">
         <v>65.55</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
       <c r="A21" s="18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C21" s="19">
         <v>66.02</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
       <c r="A22" s="18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C22" s="19">
         <v>69.2</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:4">
       <c r="A23" s="18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C23" s="19">
         <v>68</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:4">
       <c r="A24" s="18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C24" s="19">
         <v>41</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:4">
       <c r="A25" s="18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C25" s="19">
         <v>67.7</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:4">
       <c r="A26" s="18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C26" s="19">
         <v>68</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:4">
       <c r="A27" s="18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C27" s="19">
         <v>41.82</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" ht="15" spans="1:4">
@@ -2585,7 +2610,7 @@
         <v>15</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C28" s="21">
         <f>SUM(C14:C27)</f>
@@ -2600,19 +2625,19 @@
         <v>15</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C30" s="11">
         <f>C12+C28</f>
         <v>1604.27</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" ht="16.5" spans="1:4">
       <c r="A32" s="14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -2640,84 +2665,84 @@
   <sheetData>
     <row r="1" ht="38" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B3" s="5">
-        <f>支出明细表!C55</f>
-        <v>4642.7</v>
+        <f>支出明细表!C57</f>
+        <v>4932.7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:3">
       <c r="A4" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="8">
         <f>游戏变现收入明细表!C30</f>
         <v>1604.27</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B5" s="11">
         <f>B3-B4</f>
-        <v>3038.43</v>
+        <v>3328.43</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:3">
       <c r="A8" s="14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:3">
       <c r="A9" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:3">
       <c r="A10" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:3">
       <c r="A11" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:3">
       <c r="A12" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:3">

--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\MHH\now\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\MHXY\chenlong5469-ui.github.io\now\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="1" activeTab="2"/>
+    <workbookView windowHeight="17775" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="支出明细表" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="126">
   <si>
     <t>梦幻西游 · 支出明细表（黄色行为新增录入区）</t>
   </si>
@@ -289,6 +289,12 @@
   </si>
   <si>
     <t>蝴蝶仙子*2</t>
+  </si>
+  <si>
+    <t>龙鲤胚子1</t>
+  </si>
+  <si>
+    <t>龙鲤胚子2</t>
   </si>
   <si>
     <t>物品 80环装</t>
@@ -2238,7 +2244,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2380,86 +2386,78 @@
         <v>85</v>
       </c>
       <c r="C11" s="19">
-        <v>9.5</v>
+        <v>66.5</v>
       </c>
       <c r="D11" s="18" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="12" ht="15" spans="1:4">
-      <c r="A12" s="20" t="s">
+    <row r="12" ht="16.5" spans="1:4">
+      <c r="A12" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="19">
+        <v>66.5</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:4">
+      <c r="A13" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="19">
+        <v>9.5</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="14" ht="15" spans="1:4">
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="20"/>
+    </row>
+    <row r="15" ht="15" spans="1:4">
+      <c r="A15" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" s="21">
-        <f>SUM(C4:C11)</f>
-        <v>580.5</v>
-      </c>
-      <c r="D12" s="20" t="s">
+      <c r="B15" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="21">
+        <f>SUM(C4:C13)</f>
+        <v>713.5</v>
+      </c>
+      <c r="D15" s="20" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1" spans="1:4">
-      <c r="A13" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-    </row>
-    <row r="14" ht="16.5" spans="1:4">
-      <c r="A14" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="B14" s="9" t="s">
+    <row r="16" ht="26" customHeight="1" spans="1:4">
+      <c r="A16" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C14" s="8">
-        <v>202</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" spans="1:4">
-      <c r="A15" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C15" s="8">
-        <v>67.45</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:4">
-      <c r="A16" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" s="8">
-        <v>67.45</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>92</v>
-      </c>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
     </row>
     <row r="17" ht="16.5" spans="1:4">
       <c r="A17" s="9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C17" s="8">
-        <v>66.78</v>
+        <v>202</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>92</v>
@@ -2467,185 +2465,227 @@
     </row>
     <row r="18" ht="16.5" spans="1:4">
       <c r="A18" s="9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B18" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="8">
+        <v>67.45</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:4">
+      <c r="A19" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C19" s="8">
+        <v>67.45</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:4">
+      <c r="A20" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C20" s="8">
         <v>66.78</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:4">
-      <c r="A19" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="C19" s="19">
-        <v>66.02</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:4">
-      <c r="A20" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="B20" s="9" t="s">
+      <c r="D20" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:4">
+      <c r="A21" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="C20" s="19">
-        <v>65.55</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:4">
-      <c r="A21" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C21" s="19">
-        <v>66.02</v>
+      <c r="C21" s="8">
+        <v>66.78</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
       <c r="A22" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>99</v>
+        <v>90</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>98</v>
       </c>
       <c r="C22" s="19">
-        <v>69.2</v>
+        <v>66.02</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:4">
       <c r="A23" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>100</v>
+        <v>90</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="C23" s="19">
-        <v>68</v>
+        <v>65.55</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:4">
       <c r="A24" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>101</v>
+        <v>90</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>100</v>
       </c>
       <c r="C24" s="19">
-        <v>41</v>
+        <v>66.02</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:4">
       <c r="A25" s="18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C25" s="19">
-        <v>67.7</v>
+        <v>69.2</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:4">
       <c r="A26" s="18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C26" s="19">
         <v>68</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:4">
       <c r="A27" s="18" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B27" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" s="19">
+        <v>41</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" spans="1:4">
+      <c r="A28" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="C27" s="19">
+      <c r="C28" s="19">
+        <v>67.7</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" spans="1:4">
+      <c r="A29" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="19">
+        <v>68</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" ht="16.5" spans="1:4">
+      <c r="A30" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" s="19">
         <v>41.82</v>
       </c>
-      <c r="D27" s="9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="28" ht="15" spans="1:4">
-      <c r="A28" s="20" t="s">
+      <c r="D30" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" ht="15" spans="1:4">
+      <c r="A31" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="C28" s="21">
-        <f>SUM(C14:C27)</f>
+      <c r="B31" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" s="21">
+        <f>SUM(C17:C30)</f>
         <v>1023.77</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D31" s="20" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="30" ht="18" spans="1:4">
-      <c r="A30" s="22" t="s">
+    <row r="33" ht="18" spans="1:4">
+      <c r="A33" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B30" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="C30" s="11">
-        <f>C12+C28</f>
-        <v>1604.27</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="32" ht="16.5" spans="1:4">
-      <c r="A32" s="14" t="s">
+      <c r="B33" s="22" t="s">
         <v>108</v>
+      </c>
+      <c r="C33" s="11">
+        <f>C15+C31</f>
+        <v>1737.27</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" spans="1:4">
+      <c r="A35" s="14" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A35:D35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2665,84 +2705,84 @@
   <sheetData>
     <row r="1" ht="38" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B3" s="5">
         <f>支出明细表!C57</f>
         <v>4932.7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:3">
       <c r="A4" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B4" s="8">
-        <f>游戏变现收入明细表!C30</f>
-        <v>1604.27</v>
+        <f>游戏变现收入明细表!C33</f>
+        <v>1737.27</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B5" s="11">
         <f>B3-B4</f>
-        <v>3328.43</v>
+        <v>3195.43</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:3">
       <c r="A8" s="14" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:3">
       <c r="A9" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:3">
       <c r="A10" s="14" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:3">
       <c r="A11" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:3">
       <c r="A12" s="14" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:3">

--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="125">
   <si>
     <t>梦幻西游 · 支出明细表（黄色行为新增录入区）</t>
   </si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>3JN胚子  8月10</t>
+  </si>
+  <si>
+    <t>龙鲤 胚子*2</t>
   </si>
   <si>
     <t>蝴蝶仙子*2</t>
@@ -2238,7 +2241,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2366,7 +2369,7 @@
         <v>84</v>
       </c>
       <c r="C10" s="19">
-        <v>66.5</v>
+        <v>133</v>
       </c>
       <c r="D10" s="18" t="s">
         <v>79</v>
@@ -2380,94 +2383,94 @@
         <v>85</v>
       </c>
       <c r="C11" s="19">
-        <v>9.5</v>
+        <v>66.5</v>
       </c>
       <c r="D11" s="18" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="12" ht="15" spans="1:4">
-      <c r="A12" s="20" t="s">
+    <row r="12" ht="16.5" spans="1:4">
+      <c r="A12" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" s="19">
+        <v>9.5</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" ht="15" spans="1:4">
+      <c r="A13" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" s="21">
-        <f>SUM(C4:C11)</f>
-        <v>580.5</v>
-      </c>
-      <c r="D12" s="20" t="s">
+      <c r="B13" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="21">
+        <f>SUM(C4:C12)</f>
+        <v>713.5</v>
+      </c>
+      <c r="D13" s="20" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1" spans="1:4">
-      <c r="A13" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-    </row>
-    <row r="14" ht="16.5" spans="1:4">
-      <c r="A14" s="9" t="s">
+    <row r="14" ht="26" customHeight="1" spans="1:4">
+      <c r="A14" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="8">
-        <v>202</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>90</v>
-      </c>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
     </row>
     <row r="15" ht="16.5" spans="1:4">
       <c r="A15" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="8">
+        <v>202</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>91</v>
-      </c>
-      <c r="C15" s="8">
-        <v>67.45</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:4">
       <c r="A16" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16" s="8">
         <v>67.45</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
       <c r="A17" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>94</v>
       </c>
       <c r="C17" s="8">
-        <v>66.78</v>
+        <v>67.45</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
       <c r="A18" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>95</v>
@@ -2476,176 +2479,190 @@
         <v>66.78</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
-      <c r="A19" s="18" t="s">
-        <v>88</v>
+      <c r="A19" s="9" t="s">
+        <v>89</v>
       </c>
       <c r="B19" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C19" s="19">
-        <v>66.02</v>
+      <c r="C19" s="8">
+        <v>66.78</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
       <c r="A20" s="18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>97</v>
       </c>
       <c r="C20" s="19">
-        <v>65.55</v>
+        <v>66.02</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
       <c r="A21" s="18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>98</v>
       </c>
       <c r="C21" s="19">
-        <v>66.02</v>
+        <v>65.55</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
       <c r="A22" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="B22" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>99</v>
       </c>
       <c r="C22" s="19">
-        <v>69.2</v>
+        <v>66.02</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:4">
       <c r="A23" s="18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B23" s="18" t="s">
         <v>100</v>
       </c>
       <c r="C23" s="19">
-        <v>68</v>
+        <v>69.2</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:4">
       <c r="A24" s="18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B24" s="18" t="s">
         <v>101</v>
       </c>
       <c r="C24" s="19">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:4">
       <c r="A25" s="18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>102</v>
       </c>
       <c r="C25" s="19">
-        <v>67.7</v>
+        <v>41</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:4">
       <c r="A26" s="18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B26" s="18" t="s">
         <v>103</v>
       </c>
       <c r="C26" s="19">
-        <v>68</v>
+        <v>67.7</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:4">
       <c r="A27" s="18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B27" s="18" t="s">
         <v>104</v>
       </c>
       <c r="C27" s="19">
+        <v>68</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" spans="1:4">
+      <c r="A28" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="19">
         <v>41.82</v>
       </c>
-      <c r="D27" s="9" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="28" ht="15" spans="1:4">
-      <c r="A28" s="20" t="s">
+      <c r="D28" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="29" ht="15" spans="1:4">
+      <c r="A29" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="C28" s="21">
-        <f>SUM(C14:C27)</f>
+      <c r="B29" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="C29" s="21">
+        <f>SUM(C15:C28)</f>
         <v>1023.77</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D29" s="20" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="30" ht="18" spans="1:4">
-      <c r="A30" s="22" t="s">
+    <row r="31" ht="18" spans="1:4">
+      <c r="A31" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B30" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="C30" s="11">
-        <f>C12+C28</f>
-        <v>1604.27</v>
-      </c>
-      <c r="D30" s="22" t="s">
+      <c r="B31" s="22" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="32" ht="16.5" spans="1:4">
-      <c r="A32" s="14" t="s">
+      <c r="C31" s="11">
+        <f>C13+C29</f>
+        <v>1737.27</v>
+      </c>
+      <c r="D31" s="22" t="s">
         <v>108</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" spans="1:1">
+      <c r="A33" s="14" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -2665,84 +2682,84 @@
   <sheetData>
     <row r="1" ht="38" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B3" s="5">
         <f>支出明细表!C57</f>
         <v>4932.7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:3">
       <c r="A4" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B4" s="8">
-        <f>游戏变现收入明细表!C30</f>
-        <v>1604.27</v>
+        <f>游戏变现收入明细表!C31</f>
+        <v>1737.27</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B5" s="11">
         <f>B3-B4</f>
-        <v>3328.43</v>
+        <v>3195.43</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:3">
       <c r="A8" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:3">
       <c r="A9" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:3">
       <c r="A10" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:3">
       <c r="A11" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:3">
       <c r="A12" s="14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:3">

--- a/now/MHXY.xlsx
+++ b/now/MHXY.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="127">
   <si>
     <t>梦幻西游 · 支出明细表（黄色行为新增录入区）</t>
   </si>
@@ -202,6 +202,12 @@
   </si>
   <si>
     <t>法宠</t>
+  </si>
+  <si>
+    <t xml:space="preserve">龙鲤0908 </t>
+  </si>
+  <si>
+    <t>三技能女娲0908</t>
   </si>
   <si>
     <t>购宠小计</t>
@@ -2066,36 +2072,48 @@
       <c r="A43" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="18"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="18"/>
+      <c r="B43" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43" s="19">
+        <v>177</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="44" ht="16.5" spans="1:4">
       <c r="A44" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="B44" s="18"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="18"/>
+      <c r="B44" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" s="19">
+        <v>160</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="45" ht="15" spans="1:4">
       <c r="A45" s="20" t="s">
         <v>15</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C45" s="21">
         <f>SUM(C35:C44)</f>
-        <v>1204.25</v>
+        <v>1541.25</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1" spans="1:4">
       <c r="A46" s="16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
@@ -2103,49 +2121,49 @@
     </row>
     <row r="47" ht="16.5" spans="1:4">
       <c r="A47" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C47" s="8">
         <v>20</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="48" ht="16.5" spans="1:4">
       <c r="A48" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C48" s="8">
         <v>35</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:4">
       <c r="A49" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C49" s="8">
         <v>40.5</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50" ht="16.5" spans="1:4">
       <c r="A50" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B50" s="18"/>
       <c r="C50" s="19"/>
@@ -2153,7 +2171,7 @@
     </row>
     <row r="51" ht="16.5" spans="1:4">
       <c r="A51" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B51" s="18"/>
       <c r="C51" s="19"/>
@@ -2161,7 +2179,7 @@
     </row>
     <row r="52" ht="16.5" spans="1:4">
       <c r="A52" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B52" s="18"/>
       <c r="C52" s="19"/>
@@ -2169,7 +2187,7 @@
     </row>
     <row r="53" ht="16.5" spans="1:4">
       <c r="A53" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B53" s="18"/>
       <c r="C53" s="19"/>
@@ -2177,7 +2195,7 @@
     </row>
     <row r="54" ht="16.5" spans="1:4">
       <c r="A54" s="18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B54" s="18"/>
       <c r="C54" s="19"/>
@@ -2188,14 +2206,14 @@
         <v>15</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C55" s="21">
         <f>SUM(C47:C54)</f>
         <v>95.5</v>
       </c>
       <c r="D55" s="20" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="57" ht="18" spans="1:4">
@@ -2203,24 +2221,24 @@
         <v>15</v>
       </c>
       <c r="B57" s="22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C57" s="11">
         <f>C14+C33+C45+C55</f>
-        <v>4932.7</v>
+        <v>5269.7</v>
       </c>
       <c r="D57" s="22" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:4">
       <c r="A59" s="14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:4">
       <c r="A60" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2252,15 +2270,15 @@
   <sheetData>
     <row r="1" ht="38" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
@@ -2271,7 +2289,7 @@
     </row>
     <row r="3" ht="26" customHeight="1" spans="1:4">
       <c r="A3" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -2279,128 +2297,128 @@
     </row>
     <row r="4" ht="16.5" spans="1:4">
       <c r="A4" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C4" s="8">
         <v>85.5</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:4">
       <c r="A5" s="18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C5" s="19">
         <v>161.5</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:4">
       <c r="A6" s="18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C6" s="19">
         <v>123.5</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:4">
       <c r="A7" s="18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C7" s="19">
         <v>9.5</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" ht="16.5" spans="1:4">
       <c r="A8" s="18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C8" s="19">
         <v>115</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" ht="16.5" spans="1:4">
       <c r="A9" s="18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C9" s="19">
         <v>9.5</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" ht="16.5" spans="1:4">
       <c r="A10" s="18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C10" s="19">
         <v>133</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" ht="16.5" spans="1:4">
       <c r="A11" s="18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C11" s="19">
         <v>66.5</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" ht="16.5" spans="1:4">
       <c r="A12" s="18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C12" s="19">
         <v>9.5</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13" ht="15" spans="1:4">
@@ -2408,7 +2426,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C13" s="21">
         <f>SUM(C4:C12)</f>
@@ -2420,7 +2438,7 @@
     </row>
     <row r="14" ht="26" customHeight="1" spans="1:4">
       <c r="A14" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
@@ -2428,198 +2446,198 @@
     </row>
     <row r="15" ht="16.5" spans="1:4">
       <c r="A15" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C15" s="8">
         <v>202</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="1:4">
       <c r="A16" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C16" s="8">
         <v>67.45</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" ht="16.5" spans="1:4">
       <c r="A17" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C17" s="8">
         <v>67.45</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" ht="16.5" spans="1:4">
       <c r="A18" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C18" s="8">
         <v>66.78</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" ht="16.5" spans="1:4">
       <c r="A19" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C19" s="8">
         <v>66.78</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" ht="16.5" spans="1:4">
       <c r="A20" s="18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C20" s="19">
         <v>66.02</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" ht="16.5" spans="1:4">
       <c r="A21" s="18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C21" s="19">
         <v>65.55</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" ht="16.5" spans="1:4">
       <c r="A22" s="18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C22" s="19">
         <v>66.02</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" ht="16.5" spans="1:4">
       <c r="A23" s="18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C23" s="19">
         <v>69.2</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" ht="16.5" spans="1:4">
       <c r="A24" s="18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C24" s="19">
         <v>68</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" ht="16.5" spans="1:4">
       <c r="A25" s="18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C25" s="19">
         <v>41</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" ht="16.5" spans="1:4">
       <c r="A26" s="18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C26" s="19">
         <v>67.7</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" ht="16.5" spans="1:4">
       <c r="A27" s="18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C27" s="19">
         <v>68</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" ht="16.5" spans="1:4">
       <c r="A28" s="18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C28" s="19">
         <v>41.82</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" ht="15" spans="1:4">
@@ -2627,7 +2645,7 @@
         <v>15</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C29" s="21">
         <f>SUM(C15:C28)</f>
@@ -2642,19 +2660,19 @@
         <v>15</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C31" s="11">
         <f>C13+C29</f>
         <v>1737.27</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" ht="16.5" spans="1:1">
       <c r="A33" s="14" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2682,84 +2700,84 @@
   <sheetData>
     <row r="1" ht="38" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:3">
       <c r="A3" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B3" s="5">
         <f>支出明细表!C57</f>
-        <v>4932.7</v>
+        <v>5269.7</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" ht="16.5" spans="1:3">
       <c r="A4" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B4" s="8">
         <f>游戏变现收入明细表!C31</f>
         <v>1737.27</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="10" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B5" s="11">
         <f>B3-B4</f>
-        <v>3195.43</v>
+        <v>3532.43</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:3">
       <c r="A8" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:3">
       <c r="A9" s="14" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:3">
       <c r="A10" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:3">
       <c r="A11" s="14" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:3">
       <c r="A12" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" ht="16.5" spans="1:3">
